--- a/plantillas/11.xlsx
+++ b/plantillas/11.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$6</definedName>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/11.xlsx
+++ b/plantillas/11.xlsx
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/11.xlsx
+++ b/plantillas/11.xlsx
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
